--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI127"/>
+  <dimension ref="A1:BI128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46157.77083333334</v>
+        <v>46157.66666666666</v>
       </c>
     </row>
     <row r="77">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.77083333334</v>
       </c>
     </row>
     <row r="78">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46157.95833333334</v>
+        <v>46157.875</v>
       </c>
     </row>
     <row r="126">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25561,6 +25561,203 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
+        <v>46157.95833333334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Gotham FC</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI128" s="3" t="n">
         <v>46157.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>4.79</v>
+        <v>3.01</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R65" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>3.19</v>
+        <v>6.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.51</v>
+        <v>2.14</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="R70" t="n">
-        <v>6.07</v>
+        <v>3.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R72" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R65" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
         <v>3.1</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R70" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.79</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R72" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI128"/>
+  <dimension ref="A1:BI125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46157.63541666666</v>
+        <v>46157.625</v>
       </c>
     </row>
     <row r="57">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46157.64583333334</v>
+        <v>46157.63541666666</v>
       </c>
     </row>
     <row r="63">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46157.65625</v>
+        <v>46157.64583333334</v>
       </c>
     </row>
     <row r="66">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R66" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R67" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.24</v>
+        <v>4.79</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R69" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>3.19</v>
+        <v>3.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>2.14</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>2.28</v>
+        <v>3.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.05</v>
+        <v>3.57</v>
       </c>
       <c r="R73" t="n">
-        <v>4.15</v>
+        <v>2.84</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46157.66666666666</v>
+        <v>46157.65625</v>
       </c>
     </row>
     <row r="74">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46157.77083333334</v>
+        <v>46157.66666666666</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.77083333334</v>
       </c>
     </row>
     <row r="79">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="125">
@@ -24979,27 +24979,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,597 +25167,6 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI126" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI127" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI128" s="3" t="n">
         <v>46157.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.01</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>2.28</v>
+        <v>6.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R67" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>1.66</v>
+        <v>3.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.51</v>
+        <v>4.79</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="R70" t="n">
-        <v>6.07</v>
+        <v>1.66</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R72" t="n">
-        <v>3.19</v>
+        <v>2.28</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G122" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R67" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R68" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>3.93</v>
+        <v>2.28</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R73" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G122" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R66" t="n">
-        <v>3.93</v>
+        <v>2.28</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>3.19</v>
+        <v>3.93</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.01</v>
+        <v>1.51</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>2.28</v>
+        <v>6.07</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="R70" t="n">
-        <v>1.66</v>
+        <v>3.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>4.79</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R72" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.51</v>
+        <v>2.24</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R73" t="n">
-        <v>6.07</v>
+        <v>3.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="R67" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.89</v>
+        <v>4.79</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R68" t="n">
-        <v>3.93</v>
+        <v>1.66</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R70" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.79</v>
+        <v>2.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.57</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>2.84</v>
+        <v>3.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,10 +14788,10 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
         <v>3.1</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>3.93</v>
+        <v>6.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.51</v>
+        <v>2.41</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.15</v>
+        <v>3.57</v>
       </c>
       <c r="R67" t="n">
-        <v>6.07</v>
+        <v>2.84</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>4.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="R68" t="n">
-        <v>1.66</v>
+        <v>3.19</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>3.01</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.57</v>
+        <v>3.04</v>
       </c>
       <c r="R70" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>3.19</v>
+        <v>3.93</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.13</v>
+        <v>4.79</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="R73" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R67" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.14</v>
+        <v>4.79</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="R68" t="n">
-        <v>3.19</v>
+        <v>1.66</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.01</v>
+        <v>2.14</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R70" t="n">
-        <v>2.28</v>
+        <v>3.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="R72" t="n">
-        <v>3.93</v>
+        <v>2.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.79</v>
+        <v>3.01</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R73" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>2.31</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI125"/>
+  <dimension ref="A1:BI119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="R66" t="n">
-        <v>3.93</v>
+        <v>2.84</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.51</v>
+        <v>4.79</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="R67" t="n">
-        <v>6.07</v>
+        <v>1.66</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>4.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R70" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.41</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.57</v>
+        <v>3.04</v>
       </c>
       <c r="R72" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.01</v>
+        <v>2.14</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R73" t="n">
-        <v>2.28</v>
+        <v>3.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23985,1188 +23985,6 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Kaisar</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Tobol</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI120" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Floresta</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI121" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Novi Pazar</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI122" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI123" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI124" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI125" s="3" t="n">
         <v>46157.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>4.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
         <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>4.53</v>
+        <v>3.44</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.44</v>
+        <v>2.12</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.57</v>
+        <v>3.04</v>
       </c>
       <c r="R66" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4.79</v>
+        <v>3.01</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R67" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>2.14</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="R69" t="n">
-        <v>6.07</v>
+        <v>3.19</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R70" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.89</v>
+        <v>4.79</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R71" t="n">
-        <v>3.93</v>
+        <v>1.66</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R73" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI119"/>
+  <dimension ref="A1:BI111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="Q48" t="n">
         <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R66" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.01</v>
+        <v>2.41</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.04</v>
+        <v>3.57</v>
       </c>
       <c r="R67" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.14</v>
+        <v>4.79</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="R69" t="n">
-        <v>3.19</v>
+        <v>1.66</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.79</v>
+        <v>2.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R72" t="n">
-        <v>3.93</v>
+        <v>2.28</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R73" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>4.15</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21827,27 +21827,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="110">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.95833333334</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,1582 +22409,6 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Ypiranga Erechim</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Maringá</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI112" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Radnički Niš</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI113" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Confiança</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Maranhão</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI114" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Botafogo PB</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Inter de Limeira</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI115" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Anápolis</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Barra do Garcas</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI116" s="3" t="n">
-        <v>46157.875</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI117" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI118" s="3" t="n">
-        <v>46157.95833333334</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI119" s="3" t="n">
         <v>46157.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>4.53</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q46" t="n">
         <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>4.53</v>
+        <v>4.05</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
         <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
-        <v>3.44</v>
+        <v>4.53</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>3.52</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.13</v>
+        <v>3.01</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R68" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4.79</v>
+        <v>2.24</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,10 +14394,10 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
         <v>3.1</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>1.51</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R72" t="n">
-        <v>2.28</v>
+        <v>6.07</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.51</v>
+        <v>4.79</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="R73" t="n">
-        <v>6.07</v>
+        <v>1.66</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>4.15</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6123,10 +6123,10 @@
         <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q45" t="n">
         <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>4.53</v>
+        <v>4.05</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q46" t="n">
         <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>4.05</v>
+        <v>4.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="R54" t="n">
-        <v>3.52</v>
+        <v>3.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>7.65</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R66" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.89</v>
+        <v>4.79</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R70" t="n">
-        <v>3.93</v>
+        <v>1.66</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>6.07</v>
+        <v>3.1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>1.66</v>
+        <v>3.93</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6320,10 +6320,10 @@
         <v>2.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
         <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,17 +9465,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>4.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>4.53</v>
+        <v>2.12</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>3.52</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.24</v>
+        <v>4.79</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R66" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.01</v>
+        <v>1.51</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="R68" t="n">
-        <v>2.28</v>
+        <v>6.07</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.79</v>
+        <v>3.01</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.92</v>
+        <v>3.04</v>
       </c>
       <c r="R70" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="R73" t="n">
-        <v>3.93</v>
+        <v>3.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF73" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>1.94</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>4.15</v>
+        <v>2.31</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>1.94</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8093,10 +8093,10 @@
         <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,17 +9465,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>4.53</v>
+        <v>4.05</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R51" t="n">
         <v>4.53</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF51" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.79</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.12</v>
+        <v>3.44</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="R59" t="n">
-        <v>3.19</v>
+        <v>3.91</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.12</v>
+        <v>3.64</v>
       </c>
       <c r="R65" t="n">
-        <v>7.65</v>
+        <v>2.44</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>4.79</v>
+        <v>2.41</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.92</v>
+        <v>3.57</v>
       </c>
       <c r="R66" t="n">
-        <v>1.66</v>
+        <v>2.84</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.41</v>
+        <v>3.01</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.57</v>
+        <v>3.04</v>
       </c>
       <c r="R67" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>3.93</v>
+        <v>6.07</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R70" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,10 +14394,10 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
         <v>3.1</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R73" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.19</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q52" t="n">
         <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>3.44</v>
+        <v>4.53</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>2.12</v>
+        <v>3.44</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R62" t="n">
-        <v>1.82</v>
+        <v>3.91</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R67" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R68" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="R70" t="n">
-        <v>1.66</v>
+        <v>3.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>3.19</v>
+        <v>3.93</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,10 +14788,10 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
         <v>3.1</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q47" t="n">
         <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>4.05</v>
+        <v>4.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>4.53</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.43</v>
+        <v>3.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R58" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.12</v>
+        <v>3.64</v>
       </c>
       <c r="R64" t="n">
-        <v>7.65</v>
+        <v>2.44</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R66" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R68" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.01</v>
+        <v>2.24</v>
       </c>
       <c r="Q69" t="n">
         <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R70" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.41</v>
+        <v>1.89</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>2.84</v>
+        <v>3.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>4.79</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R72" t="n">
-        <v>3.93</v>
+        <v>1.66</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="R73" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>2.12</v>
+        <v>4.72</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R58" t="n">
-        <v>1.82</v>
+        <v>3.91</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="R62" t="n">
-        <v>3.91</v>
+        <v>3.19</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R66" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R67" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R68" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R69" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R73" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI111"/>
+  <dimension ref="A1:BI112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5729,10 +5729,10 @@
         <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R33" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46157.60416666666</v>
+        <v>46157.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
         <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>4.53</v>
+        <v>3.44</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46157.625</v>
+        <v>46157.60416666666</v>
       </c>
     </row>
     <row r="55">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R57" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46157.63541666666</v>
+        <v>46157.625</v>
       </c>
     </row>
     <row r="58">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>3.91</v>
+        <v>2.55</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.72</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="R60" t="n">
-        <v>1.82</v>
+        <v>3.33</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.09</v>
+        <v>3.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R62" t="n">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46157.64583333334</v>
+        <v>46157.63541666666</v>
       </c>
     </row>
     <row r="64">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>4.79</v>
+        <v>2.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.92</v>
+        <v>3.64</v>
       </c>
       <c r="R66" t="n">
-        <v>1.66</v>
+        <v>2.44</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46157.65625</v>
+        <v>46157.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R68" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>3.19</v>
+        <v>6.07</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>6.07</v>
+        <v>3.93</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,55 +14394,55 @@
         </is>
       </c>
       <c r="P71" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R71" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF71" t="n">
         <v>1.89</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R71" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>1.94</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>4.79</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="R72" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="R74" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46157.66666666666</v>
+        <v>46157.65625</v>
       </c>
     </row>
     <row r="75">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q78" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>7</v>
+        <v>2.31</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46157.77083333334</v>
+        <v>46157.66666666666</v>
       </c>
     </row>
     <row r="79">
@@ -15917,27 +15917,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,17 +15966,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46157.875</v>
+        <v>46157.77083333334</v>
       </c>
     </row>
     <row r="80">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>4.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="R109" t="n">
-        <v>1.75</v>
+        <v>6.55</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46157.95833333334</v>
+        <v>46157.875</v>
       </c>
     </row>
     <row r="110">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,141 +22274,338 @@
         </is>
       </c>
       <c r="P111" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI111" s="3" t="n">
+        <v>46157.95833333334</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q111" t="n">
+      <c r="Q112" t="n">
         <v>3.1</v>
       </c>
-      <c r="R111" t="n">
+      <c r="R112" t="n">
         <v>2.7</v>
       </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="n">
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF111" t="n">
+      <c r="AF112" t="n">
         <v>1.92</v>
       </c>
-      <c r="AG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI111" s="3" t="n">
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI112" s="3" t="n">
         <v>46157.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.19</v>
+        <v>2.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9669,10 +9669,10 @@
         <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>2.12</v>
+        <v>4.72</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>4.53</v>
+        <v>3.44</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
         <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.55</v>
+        <v>3.91</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.72</v>
+        <v>3.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R59" t="n">
-        <v>3.91</v>
+        <v>1.82</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.72</v>
+        <v>2.43</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>7.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.12</v>
+        <v>3.64</v>
       </c>
       <c r="R65" t="n">
-        <v>7.65</v>
+        <v>2.44</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.41</v>
+        <v>4.79</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.57</v>
+        <v>3.92</v>
       </c>
       <c r="R67" t="n">
-        <v>2.84</v>
+        <v>1.66</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R68" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="R69" t="n">
-        <v>6.07</v>
+        <v>2.28</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.79</v>
+        <v>1.51</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="R72" t="n">
-        <v>1.66</v>
+        <v>6.07</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.01</v>
+        <v>2.24</v>
       </c>
       <c r="Q73" t="n">
         <v>3.04</v>
       </c>
       <c r="R73" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="R74" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R78" t="n">
-        <v>2.31</v>
+        <v>4.15</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2386,70 +2386,70 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2458,52 +2458,52 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>5.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>3.69</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2655,52 +2655,52 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2977,70 +2977,70 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,52 +3049,52 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3174,70 +3174,70 @@
         <v>5.76</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4356,70 +4356,70 @@
         <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>2.89</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -4583,40 +4583,40 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5729,10 +5729,10 @@
         <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.95</v>
+        <v>4.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
         <v>4.53</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.79</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.97</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.44</v>
+        <v>2.12</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
         <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>3.52</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.72</v>
+        <v>2.09</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>1.82</v>
+        <v>3.19</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R60" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.09</v>
+        <v>3.72</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R61" t="n">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>1.66</v>
+        <v>3.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.41</v>
+        <v>4.79</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.57</v>
+        <v>3.92</v>
       </c>
       <c r="R68" t="n">
-        <v>2.84</v>
+        <v>1.66</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="R70" t="n">
-        <v>3.93</v>
+        <v>6.07</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.13</v>
+        <v>3.01</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.51</v>
+        <v>2.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.15</v>
+        <v>3.57</v>
       </c>
       <c r="R72" t="n">
-        <v>6.07</v>
+        <v>2.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R76" t="n">
-        <v>1.94</v>
+        <v>4.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>4.15</v>
+        <v>2.31</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="R88" t="n">
-        <v>3.18</v>
+        <v>6.55</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>4.45</v>
+        <v>2.45</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R111" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -810,13 +810,13 @@
         <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>4.76</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="V2" t="n">
         <v>1.31</v>
@@ -846,7 +846,7 @@
         <v>3.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -873,7 +873,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>3.17</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
         <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3568,13 +3568,13 @@
         <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,23 +5529,23 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U26" t="n">
         <v>3.4</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
@@ -5553,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD27" t="n">
         <v>3.8</v>
       </c>
-      <c r="R27" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.5</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="R36" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8296,124 +8296,124 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.53</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
         <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>4.53</v>
+        <v>3.44</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,79 +10454,79 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R51" t="n">
-        <v>2.12</v>
+        <v>4.53</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>3.44</v>
+        <v>2.12</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,80 +10848,80 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q53" t="n">
         <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>4.05</v>
+        <v>4.53</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AF53" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN53" t="n">
         <v>1.94</v>
       </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11054,40 +11054,40 @@
         <v>4.72</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
         <v>1.84</v>
@@ -11096,28 +11096,28 @@
         <v>1.92</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -11159,19 +11159,19 @@
         <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R60" t="n">
-        <v>3.91</v>
+        <v>3.33</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.82</v>
+        <v>3.91</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R66" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R67" t="n">
-        <v>3.93</v>
+        <v>2.28</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>4.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="R68" t="n">
-        <v>1.66</v>
+        <v>3.19</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="R70" t="n">
-        <v>6.07</v>
+        <v>3.1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.01</v>
+        <v>4.79</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="R71" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
       <c r="R72" t="n">
-        <v>2.84</v>
+        <v>6.07</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="R74" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>1.94</v>
+        <v>4.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R77" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R78" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="R88" t="n">
-        <v>6.55</v>
+        <v>4.61</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17782,16 +17782,16 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>

--- a/jogos_2026-05-15.xlsx
+++ b/jogos_2026-05-15.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>1.32</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AR13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AS13" t="n">
         <v>1.87</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,70 +3371,70 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,52 +3443,52 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5144,70 +5144,70 @@
         <v>7.55</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
         <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR26" t="n">
         <v>1.58</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AS26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA26" t="n">
         <v>1.98</v>
       </c>
-      <c r="AM26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
         <v>1.98</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.82</v>
+        <v>3.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="R30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="S30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6517,130 +6517,130 @@
         <v>2.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X31" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
         <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG46" t="n">
         <v>2.6</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U46" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>3.39</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AI46" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC46" t="n">
         <v>1.82</v>
       </c>
-      <c r="AL46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD46" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,83 +9662,83 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
  